--- a/research/traditional_assets/database/data/morocco/morocco_beverage_alcoholic.xlsx
+++ b/research/traditional_assets/database/data/morocco/morocco_beverage_alcoholic.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0238</v>
+        <v>0.0326</v>
       </c>
       <c r="E2">
-        <v>0.0274</v>
+        <v>0.00417</v>
       </c>
       <c r="G2">
-        <v>0.1834927382217499</v>
+        <v>0.2113997113997114</v>
       </c>
       <c r="H2">
-        <v>0.1834927382217499</v>
+        <v>0.2113997113997114</v>
       </c>
       <c r="I2">
-        <v>0.198016294721927</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="J2">
-        <v>0.1328842809570588</v>
+        <v>0.1323185011709602</v>
       </c>
       <c r="K2">
-        <v>34.3</v>
+        <v>33.4</v>
       </c>
       <c r="L2">
-        <v>0.1215019482819695</v>
+        <v>0.1204906204906205</v>
       </c>
       <c r="M2">
-        <v>33.6</v>
+        <v>31.8</v>
       </c>
       <c r="N2">
-        <v>0.03840438907303692</v>
+        <v>0.04903623747108712</v>
       </c>
       <c r="O2">
-        <v>0.979591836734694</v>
+        <v>0.9520958083832336</v>
       </c>
       <c r="P2">
-        <v>33.6</v>
+        <v>31.8</v>
       </c>
       <c r="Q2">
-        <v>0.03840438907303692</v>
+        <v>0.04903623747108712</v>
       </c>
       <c r="R2">
-        <v>0.979591836734694</v>
+        <v>0.9520958083832336</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,70 +636,70 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>14</v>
+        <v>10.4</v>
       </c>
       <c r="V2">
-        <v>0.01600182878043205</v>
+        <v>0.01603700848111025</v>
       </c>
       <c r="W2">
-        <v>0.2652745552977571</v>
+        <v>0.2368794326241135</v>
       </c>
       <c r="X2">
-        <v>0.07127094941276733</v>
+        <v>0.1226402337209028</v>
       </c>
       <c r="Y2">
-        <v>0.1940036058849898</v>
+        <v>0.1142391989032107</v>
       </c>
       <c r="Z2">
-        <v>2.384693360364926</v>
+        <v>2.162246489859594</v>
       </c>
       <c r="AA2">
-        <v>0.3168882624951655</v>
+        <v>0.2861052147003912</v>
       </c>
       <c r="AB2">
-        <v>0.07075013890030168</v>
+        <v>0.1218176050630588</v>
       </c>
       <c r="AC2">
-        <v>0.2461381235948638</v>
+        <v>0.1642876096373324</v>
       </c>
       <c r="AD2">
-        <v>11.4</v>
+        <v>7.84</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>11.4</v>
+        <v>7.84</v>
       </c>
       <c r="AG2">
-        <v>-2.6</v>
+        <v>-2.56</v>
       </c>
       <c r="AH2">
-        <v>0.012862461920343</v>
+        <v>0.01194502849133071</v>
       </c>
       <c r="AI2">
-        <v>0.07015384615384615</v>
+        <v>0.0585336717933403</v>
       </c>
       <c r="AJ2">
-        <v>-0.002980625931445603</v>
+        <v>-0.003963216397807846</v>
       </c>
       <c r="AK2">
-        <v>-0.0175084175084175</v>
+        <v>-0.02072203334952243</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1.54</v>
+        <v>-0.978</v>
       </c>
       <c r="AN2">
-        <v>0.1968911917098446</v>
+        <v>0.1438532110091743</v>
       </c>
       <c r="AP2">
-        <v>-0.04490500863557858</v>
+        <v>-0.04697247706422019</v>
       </c>
       <c r="AQ2">
-        <v>-36.2987012987013</v>
+        <v>-53.98773006134969</v>
       </c>
     </row>
     <row r="3">
@@ -719,46 +719,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0238</v>
+        <v>0.0326</v>
       </c>
       <c r="E3">
-        <v>0.0274</v>
+        <v>0.00417</v>
       </c>
       <c r="G3">
-        <v>0.1834927382217499</v>
+        <v>0.2113997113997114</v>
       </c>
       <c r="H3">
-        <v>0.1834927382217499</v>
+        <v>0.2113997113997114</v>
       </c>
       <c r="I3">
-        <v>0.198016294721927</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="J3">
-        <v>0.1328842809570588</v>
+        <v>0.1323185011709602</v>
       </c>
       <c r="K3">
-        <v>34.3</v>
+        <v>33.4</v>
       </c>
       <c r="L3">
-        <v>0.1215019482819695</v>
+        <v>0.1204906204906205</v>
       </c>
       <c r="M3">
-        <v>33.6</v>
+        <v>31.8</v>
       </c>
       <c r="N3">
-        <v>0.03840438907303692</v>
+        <v>0.04903623747108712</v>
       </c>
       <c r="O3">
-        <v>0.979591836734694</v>
+        <v>0.9520958083832336</v>
       </c>
       <c r="P3">
-        <v>33.6</v>
+        <v>31.8</v>
       </c>
       <c r="Q3">
-        <v>0.03840438907303692</v>
+        <v>0.04903623747108712</v>
       </c>
       <c r="R3">
-        <v>0.979591836734694</v>
+        <v>0.9520958083832336</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -767,70 +767,70 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>14</v>
+        <v>10.4</v>
       </c>
       <c r="V3">
-        <v>0.01600182878043205</v>
+        <v>0.01603700848111025</v>
       </c>
       <c r="W3">
-        <v>0.2652745552977571</v>
+        <v>0.2368794326241135</v>
       </c>
       <c r="X3">
-        <v>0.07127094941276733</v>
+        <v>0.1226402337209028</v>
       </c>
       <c r="Y3">
-        <v>0.1940036058849898</v>
+        <v>0.1142391989032107</v>
       </c>
       <c r="Z3">
-        <v>2.384693360364926</v>
+        <v>2.162246489859594</v>
       </c>
       <c r="AA3">
-        <v>0.3168882624951655</v>
+        <v>0.2861052147003912</v>
       </c>
       <c r="AB3">
-        <v>0.07075013890030168</v>
+        <v>0.1218176050630588</v>
       </c>
       <c r="AC3">
-        <v>0.2461381235948638</v>
+        <v>0.1642876096373324</v>
       </c>
       <c r="AD3">
-        <v>11.4</v>
+        <v>7.84</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>11.4</v>
+        <v>7.84</v>
       </c>
       <c r="AG3">
-        <v>-2.6</v>
+        <v>-2.56</v>
       </c>
       <c r="AH3">
-        <v>0.012862461920343</v>
+        <v>0.01194502849133071</v>
       </c>
       <c r="AI3">
-        <v>0.07015384615384615</v>
+        <v>0.0585336717933403</v>
       </c>
       <c r="AJ3">
-        <v>-0.002980625931445603</v>
+        <v>-0.003963216397807846</v>
       </c>
       <c r="AK3">
-        <v>-0.0175084175084175</v>
+        <v>-0.02072203334952243</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1.54</v>
+        <v>-0.978</v>
       </c>
       <c r="AN3">
-        <v>0.1968911917098446</v>
+        <v>0.1438532110091743</v>
       </c>
       <c r="AP3">
-        <v>-0.04490500863557858</v>
+        <v>-0.04697247706422019</v>
       </c>
       <c r="AQ3">
-        <v>-36.2987012987013</v>
+        <v>-53.98773006134969</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/morocco/morocco_beverage_alcoholic.xlsx
+++ b/research/traditional_assets/database/data/morocco/morocco_beverage_alcoholic.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0326</v>
+        <v>0.0424</v>
       </c>
       <c r="E2">
-        <v>0.00417</v>
+        <v>-0.00495</v>
       </c>
       <c r="G2">
-        <v>0.2113997113997114</v>
+        <v>0.2038803025320618</v>
       </c>
       <c r="H2">
-        <v>0.2113997113997114</v>
+        <v>0.2038803025320618</v>
       </c>
       <c r="I2">
-        <v>0.1904761904761905</v>
+        <v>0.2134166392634002</v>
       </c>
       <c r="J2">
-        <v>0.1323185011709602</v>
+        <v>0.1342512707576567</v>
       </c>
       <c r="K2">
-        <v>33.4</v>
+        <v>40.4</v>
       </c>
       <c r="L2">
-        <v>0.1204906204906205</v>
+        <v>0.1328510358434725</v>
       </c>
       <c r="M2">
-        <v>31.8</v>
+        <v>41.6</v>
       </c>
       <c r="N2">
-        <v>0.04903623747108712</v>
+        <v>0.06428681811157472</v>
       </c>
       <c r="O2">
-        <v>0.9520958083832336</v>
+        <v>1.02970297029703</v>
       </c>
       <c r="P2">
-        <v>31.8</v>
+        <v>41.6</v>
       </c>
       <c r="Q2">
-        <v>0.04903623747108712</v>
+        <v>0.06428681811157472</v>
       </c>
       <c r="R2">
-        <v>0.9520958083832336</v>
+        <v>1.02970297029703</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,70 +636,70 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>10.4</v>
+        <v>12.1</v>
       </c>
       <c r="V2">
-        <v>0.01603700848111025</v>
+        <v>0.01869881007572245</v>
       </c>
       <c r="W2">
-        <v>0.2368794326241135</v>
+        <v>0.3273905996758509</v>
       </c>
       <c r="X2">
-        <v>0.1226402337209028</v>
+        <v>0.09640022188252653</v>
       </c>
       <c r="Y2">
-        <v>0.1142391989032107</v>
+        <v>0.2309903777933243</v>
       </c>
       <c r="Z2">
-        <v>2.162246489859594</v>
+        <v>2.679295154185022</v>
       </c>
       <c r="AA2">
-        <v>0.2861052147003912</v>
+        <v>0.359698779184171</v>
       </c>
       <c r="AB2">
-        <v>0.1218176050630588</v>
+        <v>0.09586583190224569</v>
       </c>
       <c r="AC2">
-        <v>0.1642876096373324</v>
+        <v>0.2638329472819253</v>
       </c>
       <c r="AD2">
-        <v>7.84</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>7.84</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="AG2">
-        <v>-2.56</v>
+        <v>-3.65</v>
       </c>
       <c r="AH2">
-        <v>0.01194502849133071</v>
+        <v>0.01288993974525208</v>
       </c>
       <c r="AI2">
-        <v>0.0585336717933403</v>
+        <v>0.06233862043526375</v>
       </c>
       <c r="AJ2">
-        <v>-0.003963216397807846</v>
+        <v>-0.005672546429403995</v>
       </c>
       <c r="AK2">
-        <v>-0.02072203334952243</v>
+        <v>-0.02956662616443905</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.978</v>
+        <v>-1.2</v>
       </c>
       <c r="AN2">
-        <v>0.1438532110091743</v>
+        <v>0.127643504531722</v>
       </c>
       <c r="AP2">
-        <v>-0.04697247706422019</v>
+        <v>-0.05513595166163143</v>
       </c>
       <c r="AQ2">
-        <v>-53.98773006134969</v>
+        <v>-54.08333333333334</v>
       </c>
     </row>
     <row r="3">
@@ -719,46 +719,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0326</v>
+        <v>0.0424</v>
       </c>
       <c r="E3">
-        <v>0.00417</v>
+        <v>-0.00495</v>
       </c>
       <c r="G3">
-        <v>0.2113997113997114</v>
+        <v>0.2038803025320618</v>
       </c>
       <c r="H3">
-        <v>0.2113997113997114</v>
+        <v>0.2038803025320618</v>
       </c>
       <c r="I3">
-        <v>0.1904761904761905</v>
+        <v>0.2134166392634002</v>
       </c>
       <c r="J3">
-        <v>0.1323185011709602</v>
+        <v>0.1342512707576567</v>
       </c>
       <c r="K3">
-        <v>33.4</v>
+        <v>40.4</v>
       </c>
       <c r="L3">
-        <v>0.1204906204906205</v>
+        <v>0.1328510358434725</v>
       </c>
       <c r="M3">
-        <v>31.8</v>
+        <v>41.6</v>
       </c>
       <c r="N3">
-        <v>0.04903623747108712</v>
+        <v>0.06428681811157472</v>
       </c>
       <c r="O3">
-        <v>0.9520958083832336</v>
+        <v>1.02970297029703</v>
       </c>
       <c r="P3">
-        <v>31.8</v>
+        <v>41.6</v>
       </c>
       <c r="Q3">
-        <v>0.04903623747108712</v>
+        <v>0.06428681811157472</v>
       </c>
       <c r="R3">
-        <v>0.9520958083832336</v>
+        <v>1.02970297029703</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -767,70 +767,70 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>10.4</v>
+        <v>12.1</v>
       </c>
       <c r="V3">
-        <v>0.01603700848111025</v>
+        <v>0.01869881007572245</v>
       </c>
       <c r="W3">
-        <v>0.2368794326241135</v>
+        <v>0.3273905996758509</v>
       </c>
       <c r="X3">
-        <v>0.1226402337209028</v>
+        <v>0.09640022188252653</v>
       </c>
       <c r="Y3">
-        <v>0.1142391989032107</v>
+        <v>0.2309903777933243</v>
       </c>
       <c r="Z3">
-        <v>2.162246489859594</v>
+        <v>2.679295154185022</v>
       </c>
       <c r="AA3">
-        <v>0.2861052147003912</v>
+        <v>0.359698779184171</v>
       </c>
       <c r="AB3">
-        <v>0.1218176050630588</v>
+        <v>0.09586583190224569</v>
       </c>
       <c r="AC3">
-        <v>0.1642876096373324</v>
+        <v>0.2638329472819253</v>
       </c>
       <c r="AD3">
-        <v>7.84</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>7.84</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="AG3">
-        <v>-2.56</v>
+        <v>-3.65</v>
       </c>
       <c r="AH3">
-        <v>0.01194502849133071</v>
+        <v>0.01288993974525208</v>
       </c>
       <c r="AI3">
-        <v>0.0585336717933403</v>
+        <v>0.06233862043526375</v>
       </c>
       <c r="AJ3">
-        <v>-0.003963216397807846</v>
+        <v>-0.005672546429403995</v>
       </c>
       <c r="AK3">
-        <v>-0.02072203334952243</v>
+        <v>-0.02956662616443905</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.978</v>
+        <v>-1.2</v>
       </c>
       <c r="AN3">
-        <v>0.1438532110091743</v>
+        <v>0.127643504531722</v>
       </c>
       <c r="AP3">
-        <v>-0.04697247706422019</v>
+        <v>-0.05513595166163143</v>
       </c>
       <c r="AQ3">
-        <v>-53.98773006134969</v>
+        <v>-54.08333333333334</v>
       </c>
     </row>
   </sheetData>
